--- a/data/trans_camb/IP16A08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 14,7</t>
+          <t>-18,79; 16,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-34,64; -1,13</t>
+          <t>-34,81; -1,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 4,42</t>
+          <t>-30,23; 3,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 4,13</t>
+          <t>-22,79; 4,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 34,28</t>
+          <t>-6,91; 30,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 2,1</t>
+          <t>-25,34; 1,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 5,44</t>
+          <t>-17,9; 6,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 9,91</t>
+          <t>-14,73; 11,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,42; -1,95</t>
+          <t>-23,0; -1,64</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 94,99</t>
+          <t>-59,93; 123,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 25,23</t>
+          <t>-100,0; 20,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,7; 40,69</t>
+          <t>-89,06; 47,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-89,67; 87,94</t>
+          <t>-90,52; 85,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,99; 462,07</t>
+          <t>-30,79; 430,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 119,06</t>
+          <t>-100,0; 108,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,1; 43,69</t>
+          <t>-64,7; 47,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,63; 73,17</t>
+          <t>-61,0; 93,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,89; -8,88</t>
+          <t>-85,75; 5,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 8,07</t>
+          <t>-11,27; 8,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 15,51</t>
+          <t>-8,11; 14,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 9,39</t>
+          <t>-11,57; 9,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 20,25</t>
+          <t>-5,13; 20,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 11,16</t>
+          <t>-10,82; 11,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 13,24</t>
+          <t>-9,28; 13,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 11,13</t>
+          <t>-4,72; 10,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 10,07</t>
+          <t>-6,03; 9,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 9,71</t>
+          <t>-6,23; 9,37</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 255,15</t>
+          <t>-79,38; 219,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,96; 395,57</t>
+          <t>-57,43; 309,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,73; 254,17</t>
+          <t>-81,13; 222,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 339,63</t>
+          <t>-41,16; 381,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,0; 194,05</t>
+          <t>-68,75; 207,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,23; 228,1</t>
+          <t>-57,46; 235,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 181,35</t>
+          <t>-37,66; 161,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 162,94</t>
+          <t>-43,19; 146,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,25; 145,85</t>
+          <t>-46,23; 139,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 19,23</t>
+          <t>-7,01; 18,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 9,31</t>
+          <t>-13,11; 8,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 10,46</t>
+          <t>-10,95; 10,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 5,1</t>
+          <t>-19,98; 5,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 6,32</t>
+          <t>-22,17; 4,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 7,06</t>
+          <t>-19,37; 6,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 7,74</t>
+          <t>-10,79; 7,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 2,86</t>
+          <t>-14,71; 2,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 5,72</t>
+          <t>-13,71; 4,98</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,43; —</t>
+          <t>-70,76; 761,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,96; 447,08</t>
+          <t>-81,45; 386,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,02; 71,16</t>
+          <t>-80,93; 84,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,2; 121,83</t>
+          <t>-89,47; 79,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,28; 82,03</t>
+          <t>-78,17; 92,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 103,55</t>
+          <t>-59,59; 100,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,84; 44,34</t>
+          <t>-84,38; 48,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 72,0</t>
+          <t>-71,53; 66,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,31; -0,56</t>
+          <t>-30,73; -0,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 22,62</t>
+          <t>-16,45; 21,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 0,99</t>
+          <t>-31,13; 2,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 5,62</t>
+          <t>-21,78; 6,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 9,09</t>
+          <t>-20,57; 8,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,31; -3,59</t>
+          <t>-29,3; -4,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -1,3</t>
+          <t>-20,8; -0,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 11,56</t>
+          <t>-12,19; 11,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,26; -5,33</t>
+          <t>-24,62; -5,9</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-93,17; 17,23</t>
+          <t>-92,85; 20,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,04; 223,81</t>
+          <t>-54,18; 200,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 52,98</t>
+          <t>-100,0; 63,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 56,17</t>
+          <t>-74,31; 66,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,71; 77,2</t>
+          <t>-74,63; 73,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-94,05; -3,92</t>
+          <t>-93,9; -17,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,17; -5,19</t>
+          <t>-76,53; 2,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 78,65</t>
+          <t>-47,0; 80,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,83; -28,44</t>
+          <t>-89,02; -30,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 3,17</t>
+          <t>-9,8; 4,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 6,01</t>
+          <t>-9,26; 5,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -0,96</t>
+          <t>-13,71; -0,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 3,19</t>
+          <t>-10,07; 3,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 5,9</t>
+          <t>-9,1; 5,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 0,49</t>
+          <t>-12,45; 0,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,6</t>
+          <t>-8,1; 1,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,6</t>
+          <t>-6,57; 3,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -1,79</t>
+          <t>-11,23; -1,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,17; 27,69</t>
+          <t>-51,46; 40,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 50,37</t>
+          <t>-47,77; 52,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,9; -7,28</t>
+          <t>-74,15; 0,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 29,04</t>
+          <t>-52,22; 26,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 46,29</t>
+          <t>-45,97; 46,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 3,61</t>
+          <t>-63,05; 4,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 14,17</t>
+          <t>-44,43; 12,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 35,96</t>
+          <t>-35,86; 30,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,31; -12,29</t>
+          <t>-61,91; -12,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 16,96</t>
+          <t>-19,57; 15,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-34,81; -1,32</t>
+          <t>-32,42; -0,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 3,64</t>
+          <t>-30,28; 4,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 4,11</t>
+          <t>-22,03; 5,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 30,99</t>
+          <t>-6,01; 33,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 1,76</t>
+          <t>-25,31; 1,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 6,73</t>
+          <t>-17,18; 5,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 11,13</t>
+          <t>-14,41; 11,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,0; -1,64</t>
+          <t>-23,2; -1,33</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 123,36</t>
+          <t>-59,6; 110,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 20,55</t>
+          <t>-100,0; 13,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 47,67</t>
+          <t>-87,26; 42,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-90,52; 85,04</t>
+          <t>-89,33; 110,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 430,28</t>
+          <t>-36,33; 398,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 108,64</t>
+          <t>-100,0; 140,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,7; 47,39</t>
+          <t>-63,39; 36,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,0; 93,45</t>
+          <t>-58,35; 74,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,75; 5,26</t>
+          <t>-86,26; -2,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 8,18</t>
+          <t>-12,25; 8,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 14,42</t>
+          <t>-8,21; 14,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 9,52</t>
+          <t>-11,06; 9,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 20,32</t>
+          <t>-5,56; 20,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 11,28</t>
+          <t>-10,11; 11,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 13,57</t>
+          <t>-8,79; 14,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 10,84</t>
+          <t>-5,2; 11,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 9,74</t>
+          <t>-4,9; 10,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 9,37</t>
+          <t>-6,1; 9,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,38; 219,19</t>
+          <t>-81,03; 205,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 309,24</t>
+          <t>-59,32; 322,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,13; 222,56</t>
+          <t>-79,69; 222,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 381,38</t>
+          <t>-40,17; 328,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,75; 207,05</t>
+          <t>-67,06; 201,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,46; 235,03</t>
+          <t>-55,42; 279,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 161,04</t>
+          <t>-38,04; 189,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 146,04</t>
+          <t>-38,89; 151,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 139,46</t>
+          <t>-45,47; 150,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 18,4</t>
+          <t>-6,16; 19,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 8,99</t>
+          <t>-12,27; 11,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 10,39</t>
+          <t>-12,55; 10,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 5,05</t>
+          <t>-20,32; 5,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 4,52</t>
+          <t>-21,17; 4,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 6,91</t>
+          <t>-18,95; 7,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 7,31</t>
+          <t>-10,22; 7,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 2,94</t>
+          <t>-14,08; 3,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 4,98</t>
+          <t>-12,18; 5,1</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 761,06</t>
+          <t>-57,54; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,45; 386,17</t>
+          <t>-80,83; 391,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,93; 84,34</t>
+          <t>-84,61; 60,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-89,47; 79,98</t>
+          <t>-100,0; 78,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,17; 92,93</t>
+          <t>-76,7; 99,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,59; 100,09</t>
+          <t>-59,99; 94,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,38; 48,76</t>
+          <t>-81,23; 56,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,53; 66,42</t>
+          <t>-69,76; 58,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,73; -0,46</t>
+          <t>-30,98; -0,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 21,37</t>
+          <t>-14,99; 22,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 2,35</t>
+          <t>-30,15; 0,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 6,96</t>
+          <t>-20,95; 6,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 8,99</t>
+          <t>-22,38; 8,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,3; -4,37</t>
+          <t>-28,57; -3,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-20,8; -0,7</t>
+          <t>-21,74; 0,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 11,91</t>
+          <t>-13,44; 9,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-24,62; -5,9</t>
+          <t>-25,63; -4,88</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-92,85; 20,35</t>
+          <t>-93,14; 25,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 200,43</t>
+          <t>-50,3; 208,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,93</t>
+          <t>-100,0; 39,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,31; 66,01</t>
+          <t>-72,26; 54,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 73,41</t>
+          <t>-79,38; 67,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-93,9; -17,67</t>
+          <t>-93,85; -2,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,53; 2,98</t>
+          <t>-76,74; 5,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 80,17</t>
+          <t>-51,81; 64,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-89,02; -30,43</t>
+          <t>-89,49; -28,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 4,34</t>
+          <t>-10,43; 2,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 5,87</t>
+          <t>-8,83; 6,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,03</t>
+          <t>-14,55; -0,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 3,36</t>
+          <t>-10,08; 2,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 5,71</t>
+          <t>-9,09; 6,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 0,44</t>
+          <t>-12,48; 0,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 1,63</t>
+          <t>-8,57; 1,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 3,9</t>
+          <t>-6,41; 4,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -1,8</t>
+          <t>-11,46; -2,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 40,41</t>
+          <t>-54,05; 27,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 52,28</t>
+          <t>-47,38; 55,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 0,03</t>
+          <t>-74,8; -6,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,22; 26,0</t>
+          <t>-50,24; 25,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 46,43</t>
+          <t>-45,31; 51,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 4,68</t>
+          <t>-61,83; 7,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 12,35</t>
+          <t>-45,18; 10,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 30,23</t>
+          <t>-34,73; 31,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,91; -12,72</t>
+          <t>-61,37; -15,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-7,68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-10,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-17,92</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-13,48</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,3</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-10,63</t>
+          <t>-13,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,5</t>
+          <t>-11,85</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 15,85</t>
+          <t>-22,7; 4,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-32,42; -0,6</t>
+          <t>-5,01; 34,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 4,13</t>
+          <t>-23,74; 3,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 5,55</t>
+          <t>-20,26; 14,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 33,35</t>
+          <t>-34,64; -1,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 1,3</t>
+          <t>-28,64; 5,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 5,01</t>
+          <t>-17,69; 5,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 11,23</t>
+          <t>-14,39; 9,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,2; -1,33</t>
+          <t>-23,06; -0,89</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-49,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-65,73%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-9,97%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-71,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-53,44%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-49,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>85,11%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-68,02%</t>
+          <t>-51,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-60,21%</t>
+          <t>-57,11%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 110,91</t>
+          <t>-89,67; 87,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,82</t>
+          <t>-30,99; 462,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-87,26; 42,76</t>
+          <t>-100,0; 117,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-89,33; 110,95</t>
+          <t>-62,03; 94,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 398,29</t>
+          <t>-100,0; 25,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 140,38</t>
+          <t>-88,0; 47,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 36,96</t>
+          <t>-65,1; 43,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 74,23</t>
+          <t>-59,63; 73,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,26; -2,69</t>
+          <t>-84,51; -0,88</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,76</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,99</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>2,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 8,35</t>
+          <t>-5,89; 20,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 14,53</t>
+          <t>-12,15; 11,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 9,41</t>
+          <t>-7,62; 13,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 20,27</t>
+          <t>-11,13; 8,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 11,08</t>
+          <t>-6,29; 15,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 14,38</t>
+          <t>-8,52; 12,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 11,51</t>
+          <t>-5,56; 11,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 10,08</t>
+          <t>-5,01; 10,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 9,9</t>
+          <t>-6,08; 10,6</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-16,01%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>42,16%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-11,07%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,03; 205,02</t>
+          <t>-39,62; 339,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 322,8</t>
+          <t>-68,0; 194,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,69; 222,98</t>
+          <t>-53,29; 238,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 328,89</t>
+          <t>-79,78; 255,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,06; 201,04</t>
+          <t>-47,96; 395,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 279,15</t>
+          <t>-73,04; 315,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,04; 189,67</t>
+          <t>-40,55; 181,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 151,68</t>
+          <t>-37,35; 162,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 150,97</t>
+          <t>-43,85; 161,89</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-7,18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-8,73</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,36</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,67</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-8,73</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,35</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-0,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 19,81</t>
+          <t>-21,04; 5,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 11,04</t>
+          <t>-21,14; 6,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 10,37</t>
+          <t>-18,47; 7,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 5,03</t>
+          <t>-5,48; 19,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 4,59</t>
+          <t>-12,53; 9,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 7,24</t>
+          <t>-6,46; 16,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 7,33</t>
+          <t>-11,64; 7,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 3,41</t>
+          <t>-15,14; 2,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 5,1</t>
+          <t>-9,55; 7,91</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-43,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-52,29%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-29,5%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>84,95%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-8,88%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-43,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-52,29%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-32,04%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-27,18%</t>
+          <t>-5,68%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,54; —</t>
+          <t>-82,02; 71,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-92,2; 121,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,83; 391,0</t>
+          <t>-76,2; 94,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-84,61; 60,34</t>
+          <t>-57,43; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 78,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 99,37</t>
+          <t>-64,37; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 94,45</t>
+          <t>-61,83; 103,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,23; 56,94</t>
+          <t>-84,84; 44,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,76; 58,36</t>
+          <t>-55,41; 112,92</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-8,12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-7,19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-16,24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-13,81</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,56</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-13,46</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-8,12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-7,19</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-16,09</t>
+          <t>-13,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-14,94</t>
+          <t>-14,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,98; -0,42</t>
+          <t>-20,44; 5,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 22,13</t>
+          <t>-21,62; 9,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 0,81</t>
+          <t>-29,33; -3,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 6,54</t>
+          <t>-30,31; -0,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 8,96</t>
+          <t>-16,4; 22,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,57; -3,93</t>
+          <t>-31,99; 1,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 0,36</t>
+          <t>-21,32; -1,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 9,81</t>
+          <t>-12,67; 11,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,63; -4,88</t>
+          <t>-25,76; -5,39</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-37,23%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-32,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-74,47%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-67,45%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>22,29%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-65,73%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-37,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-32,97%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-73,76%</t>
+          <t>-65,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-70,22%</t>
+          <t>-70,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-93,14; 25,74</t>
+          <t>-71,09; 56,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,3; 208,18</t>
+          <t>-76,71; 77,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,09</t>
+          <t>-94,26; -4,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-72,26; 54,73</t>
+          <t>-93,17; 17,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,38; 67,22</t>
+          <t>-56,04; 223,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-93,85; -2,68</t>
+          <t>-96,93; 55,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,74; 5,17</t>
+          <t>-78,17; -5,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 64,05</t>
+          <t>-49,68; 78,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-89,49; -28,42</t>
+          <t>-89,16; -28,35</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-3,58</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-3,39</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,63</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-7,02</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-4,62</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,55</t>
+          <t>-5,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 2,88</t>
+          <t>-9,92; 3,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 6,24</t>
+          <t>-8,46; 5,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -0,56</t>
+          <t>-12,79; 0,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 2,99</t>
+          <t>-10,6; 3,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 6,11</t>
+          <t>-9,21; 6,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 0,74</t>
+          <t>-11,67; 2,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 1,38</t>
+          <t>-8,18; 1,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 4,03</t>
+          <t>-6,51; 4,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -2,28</t>
+          <t>-10,28; -0,3</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-21,99%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-8,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-36,33%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-21,95%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-10,54%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-45,44%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-21,99%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-8,87%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-37,21%</t>
+          <t>-29,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-41,25%</t>
+          <t>-33,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 27,86</t>
+          <t>-50,5; 29,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 55,38</t>
+          <t>-41,9; 46,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,8; -6,13</t>
+          <t>-63,63; 6,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 25,11</t>
+          <t>-52,17; 27,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,31; 51,59</t>
+          <t>-48,12; 50,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 7,15</t>
+          <t>-62,25; 21,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 10,24</t>
+          <t>-44,94; 14,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 31,52</t>
+          <t>-35,98; 35,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,37; -15,04</t>
+          <t>-55,93; -2,26</t>
         </is>
       </c>
     </row>
